--- a/output/yearly_benthic_cover_iteration_35_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_35_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.74125652634466</v>
+        <v>45.74640658533961</v>
       </c>
       <c r="M2" t="n">
-        <v>99.01194218752039</v>
+        <v>98.68386969896602</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.95263186071962</v>
+        <v>87.98713047504685</v>
       </c>
       <c r="C3" t="n">
-        <v>45.88600888688438</v>
+        <v>45.9290713409773</v>
       </c>
       <c r="D3" t="n">
-        <v>2.22857129349266</v>
+        <v>2.228627211548904</v>
       </c>
       <c r="E3" t="n">
-        <v>5.67792105072396</v>
+        <v>5.704294349918538</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428570978308866</v>
+        <v>0.7428757371829682</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95908479889399</v>
+        <v>33.97369361454665</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17142650022078</v>
+        <v>34.17228391041653</v>
       </c>
       <c r="I3" t="n">
-        <v>6.529914258114299</v>
+        <v>6.522382294039708</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642856861443041</v>
+        <v>4.642973357393551</v>
       </c>
       <c r="K3" t="n">
-        <v>12.04736813928039</v>
+        <v>12.01286952495315</v>
       </c>
       <c r="L3" t="n">
-        <v>48.83221578113087</v>
+        <v>48.82392819426085</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7655928072956</v>
+        <v>106.7658690601913</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.94544714934958</v>
+        <v>86.96727312750544</v>
       </c>
       <c r="C4" t="n">
-        <v>42.50818206542067</v>
+        <v>42.53551999538339</v>
       </c>
       <c r="D4" t="n">
-        <v>2.179504153047024</v>
+        <v>2.178929707885865</v>
       </c>
       <c r="E4" t="n">
-        <v>6.461737057988739</v>
+        <v>6.48486843211248</v>
       </c>
       <c r="F4" t="n">
-        <v>0.744410094005853</v>
+        <v>0.7444265871037126</v>
       </c>
       <c r="G4" t="n">
-        <v>33.21139717135519</v>
+        <v>33.21609370994778</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24286432426924</v>
+        <v>34.24362300677078</v>
       </c>
       <c r="I4" t="n">
-        <v>5.452971261146952</v>
+        <v>5.446665514286615</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652563087536581</v>
+        <v>4.652666169398204</v>
       </c>
       <c r="K4" t="n">
-        <v>13.05455285065042</v>
+        <v>13.03272687249457</v>
       </c>
       <c r="L4" t="n">
-        <v>44.25587857675907</v>
+        <v>44.25057584617651</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81861349283017</v>
+        <v>99.81882271405446</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.62590690409439</v>
+        <v>85.59941409996046</v>
       </c>
       <c r="C5" t="n">
-        <v>42.03486535074536</v>
+        <v>42.01294073093354</v>
       </c>
       <c r="D5" t="n">
-        <v>2.114528793237881</v>
+        <v>2.11149469999921</v>
       </c>
       <c r="E5" t="n">
-        <v>7.027799057629605</v>
+        <v>7.041991048979308</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457292820915842</v>
+        <v>0.7457446847343752</v>
       </c>
       <c r="G5" t="n">
-        <v>32.22129927319047</v>
+        <v>32.18809930829838</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30354697621288</v>
+        <v>34.30425549778126</v>
       </c>
       <c r="I5" t="n">
-        <v>4.552195508659577</v>
+        <v>4.546924580578082</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660808013072401</v>
+        <v>4.660904279589845</v>
       </c>
       <c r="K5" t="n">
-        <v>14.3740930959056</v>
+        <v>14.40058590003955</v>
       </c>
       <c r="L5" t="n">
-        <v>43.43957012942828</v>
+        <v>43.43517710474116</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84852857607925</v>
+        <v>99.84870373571425</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.07979330106713</v>
+        <v>84.04063239227523</v>
       </c>
       <c r="C6" t="n">
-        <v>41.19549217932496</v>
+        <v>41.16006533718414</v>
       </c>
       <c r="D6" t="n">
-        <v>2.038556552086405</v>
+        <v>2.034939214089274</v>
       </c>
       <c r="E6" t="n">
-        <v>7.40850113699365</v>
+        <v>7.419140668995332</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468524937569663</v>
+        <v>0.7468671406436811</v>
       </c>
       <c r="G6" t="n">
-        <v>31.06363032754876</v>
+        <v>31.02107029180832</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35521471282046</v>
+        <v>34.35588846960933</v>
       </c>
       <c r="I6" t="n">
-        <v>3.799209991879834</v>
+        <v>3.794806978106293</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667828085981039</v>
+        <v>4.667919629023007</v>
       </c>
       <c r="K6" t="n">
-        <v>15.9202066989329</v>
+        <v>15.95936760772475</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75785124650159</v>
+        <v>42.7542635945195</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87355012475945</v>
+        <v>99.87369653942839</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.35737640978388</v>
+        <v>82.21955435419916</v>
       </c>
       <c r="C7" t="n">
-        <v>40.06279167353035</v>
+        <v>39.92799580219751</v>
       </c>
       <c r="D7" t="n">
-        <v>1.954386408372252</v>
+        <v>1.945876971754638</v>
       </c>
       <c r="E7" t="n">
-        <v>7.6309559526599</v>
+        <v>7.622163690710739</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478107463356682</v>
+        <v>0.7478259065394706</v>
       </c>
       <c r="G7" t="n">
-        <v>29.78104131804736</v>
+        <v>29.66338547219305</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39929433144074</v>
+        <v>34.39999170081564</v>
       </c>
       <c r="I7" t="n">
-        <v>3.170070488330042</v>
+        <v>3.166398696313941</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673817164597926</v>
+        <v>4.673911915871691</v>
       </c>
       <c r="K7" t="n">
-        <v>17.6426235902161</v>
+        <v>17.78044564580084</v>
       </c>
       <c r="L7" t="n">
-        <v>42.18905112536802</v>
+        <v>42.18614724705424</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89446638911447</v>
+        <v>99.89458869505258</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.14220907238888</v>
+        <v>87.16927196563672</v>
       </c>
       <c r="C8" t="n">
-        <v>42.32020005966998</v>
+        <v>42.271557855287</v>
       </c>
       <c r="D8" t="n">
-        <v>1.958554429897503</v>
+        <v>1.950079730787592</v>
       </c>
       <c r="E8" t="n">
-        <v>9.43077662806583</v>
+        <v>9.483915134927503</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494055646756796</v>
+        <v>0.7494410816658568</v>
       </c>
       <c r="G8" t="n">
-        <v>30.27171759764424</v>
+        <v>30.17942119053908</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47265597508127</v>
+        <v>34.47428975662941</v>
       </c>
       <c r="I8" t="n">
-        <v>5.57531409780135</v>
+        <v>5.648118310675677</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683784779222997</v>
+        <v>4.684006760411605</v>
       </c>
       <c r="K8" t="n">
-        <v>12.85779092761112</v>
+        <v>12.83072803436326</v>
       </c>
       <c r="L8" t="n">
-        <v>44.63656070572921</v>
+        <v>44.70984925571548</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81455169301032</v>
+        <v>99.81213514536574</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84.91232918067605</v>
+        <v>84.88989757908038</v>
       </c>
       <c r="C9" t="n">
-        <v>40.95492350882061</v>
+        <v>40.86794362784642</v>
       </c>
       <c r="D9" t="n">
-        <v>1.857111254726112</v>
+        <v>1.84667713560545</v>
       </c>
       <c r="E9" t="n">
-        <v>9.718074362501117</v>
+        <v>9.766945784600862</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507748874212379</v>
+        <v>0.7508287515708582</v>
       </c>
       <c r="G9" t="n">
-        <v>28.70379632667021</v>
+        <v>28.57916330214171</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53564482137695</v>
+        <v>34.53812257225947</v>
       </c>
       <c r="I9" t="n">
-        <v>4.654584481597692</v>
+        <v>4.715480335584159</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692343046382736</v>
+        <v>4.692679697317864</v>
       </c>
       <c r="K9" t="n">
-        <v>15.08767081932395</v>
+        <v>15.11010242091962</v>
       </c>
       <c r="L9" t="n">
-        <v>43.80253583580539</v>
+        <v>43.86506177593741</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84513016394995</v>
+        <v>99.84310782470345</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.45789871413474</v>
+        <v>82.36751586894304</v>
       </c>
       <c r="C10" t="n">
-        <v>39.22179643166596</v>
+        <v>39.07616108816822</v>
       </c>
       <c r="D10" t="n">
-        <v>1.746685568444709</v>
+        <v>1.73354185765898</v>
       </c>
       <c r="E10" t="n">
-        <v>9.787713298515653</v>
+        <v>9.824552225715539</v>
       </c>
       <c r="F10" t="n">
-        <v>0.751953951474257</v>
+        <v>0.752024664479477</v>
       </c>
       <c r="G10" t="n">
-        <v>26.99703998658135</v>
+        <v>26.82828247878367</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58988176781583</v>
+        <v>34.59313456605594</v>
       </c>
       <c r="I10" t="n">
-        <v>3.884911944588851</v>
+        <v>3.935825923252694</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699712196714105</v>
+        <v>4.700154152996732</v>
       </c>
       <c r="K10" t="n">
-        <v>17.54210128586524</v>
+        <v>17.63248413105696</v>
       </c>
       <c r="L10" t="n">
-        <v>43.1068082690911</v>
+        <v>43.16036921589747</v>
       </c>
       <c r="M10" t="n">
-        <v>99.8707059866223</v>
+        <v>99.86901443512266</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>79.97173923259265</v>
+        <v>79.84549056877036</v>
       </c>
       <c r="C11" t="n">
-        <v>37.33680442688897</v>
+        <v>37.16301841580562</v>
       </c>
       <c r="D11" t="n">
-        <v>1.636192266784998</v>
+        <v>1.621867077650598</v>
       </c>
       <c r="E11" t="n">
-        <v>9.708854102865455</v>
+        <v>9.739046500866616</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529700125588692</v>
+        <v>0.7530557866803954</v>
       </c>
       <c r="G11" t="n">
-        <v>25.28923857283706</v>
+        <v>25.10000431198657</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63662057770799</v>
+        <v>34.64056618729819</v>
       </c>
       <c r="I11" t="n">
-        <v>3.241801121345341</v>
+        <v>3.284352037535506</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706062578492931</v>
+        <v>4.706598666752472</v>
       </c>
       <c r="K11" t="n">
-        <v>20.02826076740736</v>
+        <v>20.15450943122965</v>
       </c>
       <c r="L11" t="n">
-        <v>42.52702058502064</v>
+        <v>42.57314365509659</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89208577931696</v>
+        <v>99.89067150213187</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.34442568006003</v>
+        <v>77.29191646194039</v>
       </c>
       <c r="C12" t="n">
-        <v>35.21019155825619</v>
+        <v>35.11655957556748</v>
       </c>
       <c r="D12" t="n">
-        <v>1.520619322057271</v>
+        <v>1.510060526282853</v>
       </c>
       <c r="E12" t="n">
-        <v>9.473841183795384</v>
+        <v>9.524365521746565</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538476971238566</v>
+        <v>0.7539457112554865</v>
       </c>
       <c r="G12" t="n">
-        <v>23.50292541690961</v>
+        <v>23.36968685249171</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67699406769741</v>
+        <v>34.68150271775238</v>
       </c>
       <c r="I12" t="n">
-        <v>2.704649885452396</v>
+        <v>2.740194437064603</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711548107024102</v>
+        <v>4.712160695346791</v>
       </c>
       <c r="K12" t="n">
-        <v>22.65557431993997</v>
+        <v>22.70808353805963</v>
       </c>
       <c r="L12" t="n">
-        <v>42.04418409065537</v>
+        <v>42.08412488533025</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90994996885152</v>
+        <v>99.90876799895734</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>74.89027386145979</v>
+        <v>74.78548133231035</v>
       </c>
       <c r="C13" t="n">
-        <v>33.17272761870982</v>
+        <v>33.03220604285001</v>
       </c>
       <c r="D13" t="n">
-        <v>1.413860490881161</v>
+        <v>1.401474843328915</v>
       </c>
       <c r="E13" t="n">
-        <v>9.18472982955714</v>
+        <v>9.220456176535274</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546047089175045</v>
+        <v>0.7547138574982276</v>
       </c>
       <c r="G13" t="n">
-        <v>21.85284455161197</v>
+        <v>21.68921553155464</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71181661020522</v>
+        <v>34.71683744491847</v>
       </c>
       <c r="I13" t="n">
-        <v>2.256138239552388</v>
+        <v>2.285821869110917</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716279430734402</v>
+        <v>4.716961609363922</v>
       </c>
       <c r="K13" t="n">
-        <v>25.10972613854021</v>
+        <v>25.21451866768964</v>
       </c>
       <c r="L13" t="n">
-        <v>41.64241707926517</v>
+        <v>41.67715877731967</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92487083651521</v>
+        <v>99.92388348785931</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.35334027056669</v>
+        <v>82.25083599276627</v>
       </c>
       <c r="C14" t="n">
-        <v>37.95319511211336</v>
+        <v>37.82011592898806</v>
       </c>
       <c r="D14" t="n">
-        <v>1.415427528751522</v>
+        <v>1.403042867591186</v>
       </c>
       <c r="E14" t="n">
-        <v>11.79930684173401</v>
+        <v>11.84062330376986</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554410673585623</v>
+        <v>0.7555582605535249</v>
       </c>
       <c r="G14" t="n">
-        <v>24.02508471139667</v>
+        <v>23.86320610561665</v>
       </c>
       <c r="H14" t="n">
-        <v>36.89830888066115</v>
+        <v>36.90540382627169</v>
       </c>
       <c r="I14" t="n">
-        <v>2.738264569673752</v>
+        <v>2.760762500503835</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721506670991013</v>
+        <v>4.722239128459531</v>
       </c>
       <c r="K14" t="n">
-        <v>17.64665972943331</v>
+        <v>17.74916400723372</v>
       </c>
       <c r="L14" t="n">
-        <v>44.30897072505189</v>
+        <v>44.33879749362172</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90882556659857</v>
+        <v>99.9080774298435</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.52364565075362</v>
+        <v>81.41081338710453</v>
       </c>
       <c r="C15" t="n">
-        <v>37.5458800529935</v>
+        <v>37.40034610841444</v>
       </c>
       <c r="D15" t="n">
-        <v>1.385184528347289</v>
+        <v>1.371949245407459</v>
       </c>
       <c r="E15" t="n">
-        <v>11.92786441173153</v>
+        <v>11.96752360810548</v>
       </c>
       <c r="F15" t="n">
-        <v>0.756146564562845</v>
+        <v>0.756270656931783</v>
       </c>
       <c r="G15" t="n">
-        <v>23.51174818806411</v>
+        <v>23.33986641878179</v>
       </c>
       <c r="H15" t="n">
-        <v>36.93276776154922</v>
+        <v>36.94570722522668</v>
       </c>
       <c r="I15" t="n">
-        <v>2.284018167980853</v>
+        <v>2.302804626827712</v>
       </c>
       <c r="J15" t="n">
-        <v>4.72591602851778</v>
+        <v>4.726691605823644</v>
       </c>
       <c r="K15" t="n">
-        <v>18.47635434924638</v>
+        <v>18.58918661289546</v>
       </c>
       <c r="L15" t="n">
-        <v>43.90170269304696</v>
+        <v>43.93377943145389</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92393709528683</v>
+        <v>99.92331215276378</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.99449666750411</v>
+        <v>78.79580074964161</v>
       </c>
       <c r="C16" t="n">
-        <v>35.36901945500917</v>
+        <v>35.14043126771186</v>
       </c>
       <c r="D16" t="n">
-        <v>1.291086174885629</v>
+        <v>1.275172843334192</v>
       </c>
       <c r="E16" t="n">
-        <v>11.43506047451554</v>
+        <v>11.4434361530126</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567543567975156</v>
+        <v>0.7568850997535759</v>
       </c>
       <c r="G16" t="n">
-        <v>21.91454814270864</v>
+        <v>21.69348751340943</v>
       </c>
       <c r="H16" t="n">
-        <v>36.96245439969898</v>
+        <v>36.97572428908143</v>
       </c>
       <c r="I16" t="n">
-        <v>1.904878388913335</v>
+        <v>1.920562977590516</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729714729984472</v>
+        <v>4.730531873459849</v>
       </c>
       <c r="K16" t="n">
-        <v>21.00550333249588</v>
+        <v>21.2041992503584</v>
       </c>
       <c r="L16" t="n">
-        <v>43.56203226338438</v>
+        <v>43.59140268674008</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93655505088942</v>
+        <v>99.93603320481034</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.91473627214862</v>
+        <v>80.75932561056635</v>
       </c>
       <c r="C17" t="n">
-        <v>36.76381440511872</v>
+        <v>36.57598851962146</v>
       </c>
       <c r="D17" t="n">
-        <v>1.29208101912385</v>
+        <v>1.276156212211828</v>
       </c>
       <c r="E17" t="n">
-        <v>12.28345257228784</v>
+        <v>12.3120038516571</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573374725695321</v>
+        <v>0.7574687831773051</v>
       </c>
       <c r="G17" t="n">
-        <v>22.4592716352881</v>
+        <v>22.25856580084009</v>
       </c>
       <c r="H17" t="n">
-        <v>37.51877303064199</v>
+        <v>37.55258770517477</v>
       </c>
       <c r="I17" t="n">
-        <v>1.870461338677728</v>
+        <v>1.868363362647091</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733359203559575</v>
+        <v>4.734179894858157</v>
       </c>
       <c r="K17" t="n">
-        <v>19.08526372785138</v>
+        <v>19.24067438943365</v>
       </c>
       <c r="L17" t="n">
-        <v>44.08862116144251</v>
+        <v>44.12110630240636</v>
       </c>
       <c r="M17" t="n">
-        <v>99.9376992944126</v>
+        <v>99.93776921146147</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.4834184476273</v>
+        <v>78.24396036508446</v>
       </c>
       <c r="C18" t="n">
-        <v>34.62061117178659</v>
+        <v>34.34832431388321</v>
       </c>
       <c r="D18" t="n">
-        <v>1.205700730176388</v>
+        <v>1.187395909417343</v>
       </c>
       <c r="E18" t="n">
-        <v>11.72221773823827</v>
+        <v>11.7153360309958</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7578391740414332</v>
+        <v>0.7579715434098977</v>
       </c>
       <c r="G18" t="n">
-        <v>20.9577881023737</v>
+        <v>20.71041909172419</v>
       </c>
       <c r="H18" t="n">
-        <v>37.54362750349612</v>
+        <v>37.57751275574901</v>
       </c>
       <c r="I18" t="n">
-        <v>1.559750361542445</v>
+        <v>1.558002887476345</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736494837758957</v>
+        <v>4.737322146311861</v>
       </c>
       <c r="K18" t="n">
-        <v>21.51658155237269</v>
+        <v>21.75603963491553</v>
       </c>
       <c r="L18" t="n">
-        <v>43.810850016433</v>
+        <v>43.8437370689055</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94804274059227</v>
+        <v>99.94810101770425</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.55367391927447</v>
+        <v>77.26541315835351</v>
       </c>
       <c r="C19" t="n">
-        <v>33.91913874921364</v>
+        <v>33.59943706998152</v>
       </c>
       <c r="D19" t="n">
-        <v>1.172813148929936</v>
+        <v>1.153088002585927</v>
       </c>
       <c r="E19" t="n">
-        <v>11.62105071229826</v>
+        <v>11.5948891211554</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7582663519382268</v>
+        <v>0.7583993543262201</v>
       </c>
       <c r="G19" t="n">
-        <v>20.38612803639539</v>
+        <v>20.11202463625812</v>
       </c>
       <c r="H19" t="n">
-        <v>37.56479005141433</v>
+        <v>37.59872208782081</v>
       </c>
       <c r="I19" t="n">
-        <v>1.311460918684414</v>
+        <v>1.308293991668159</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739164699613917</v>
+        <v>4.739995964538876</v>
       </c>
       <c r="K19" t="n">
-        <v>22.44632608072554</v>
+        <v>22.73458684164649</v>
       </c>
       <c r="L19" t="n">
-        <v>43.59084443364772</v>
+        <v>43.62239088881355</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9563092635869</v>
+        <v>99.95641480044156</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.9530144332476</v>
+        <v>74.67521910285394</v>
       </c>
       <c r="C20" t="n">
-        <v>31.51974611335225</v>
+        <v>31.2099145576689</v>
       </c>
       <c r="D20" t="n">
-        <v>1.081413240101629</v>
+        <v>1.062712866457483</v>
       </c>
       <c r="E20" t="n">
-        <v>10.89763258661893</v>
+        <v>10.86791691536946</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7586350719126591</v>
+        <v>0.7587686172471644</v>
       </c>
       <c r="G20" t="n">
-        <v>18.79739223002351</v>
+        <v>18.5357121950184</v>
       </c>
       <c r="H20" t="n">
-        <v>37.58305657265968</v>
+        <v>37.61702882010206</v>
       </c>
       <c r="I20" t="n">
-        <v>1.093415532477086</v>
+        <v>1.09077583086459</v>
       </c>
       <c r="J20" t="n">
-        <v>4.741469199454119</v>
+        <v>4.742303857794778</v>
       </c>
       <c r="K20" t="n">
-        <v>25.04698556675238</v>
+        <v>25.32478089714606</v>
       </c>
       <c r="L20" t="n">
-        <v>43.39683884993192</v>
+        <v>43.42896304541649</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96357053003656</v>
+        <v>99.96365850023145</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.20293812820731</v>
+        <v>81.07247367578995</v>
       </c>
       <c r="C21" t="n">
-        <v>35.50493412933347</v>
+        <v>35.30601233548475</v>
       </c>
       <c r="D21" t="n">
-        <v>1.08206246705452</v>
+        <v>1.063341823158715</v>
       </c>
       <c r="E21" t="n">
-        <v>13.01217269612233</v>
+        <v>13.035962452236</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7590905188388022</v>
+        <v>0.7592176873784906</v>
       </c>
       <c r="G21" t="n">
-        <v>20.67292385140446</v>
+        <v>20.46838590691751</v>
       </c>
       <c r="H21" t="n">
-        <v>39.46986617656104</v>
+        <v>39.5609956313307</v>
       </c>
       <c r="I21" t="n">
-        <v>1.462506675483644</v>
+        <v>1.439459628652965</v>
       </c>
       <c r="J21" t="n">
-        <v>4.744315742742513</v>
+        <v>4.745110546115567</v>
       </c>
       <c r="K21" t="n">
-        <v>18.79706187179269</v>
+        <v>18.92752632421004</v>
       </c>
       <c r="L21" t="n">
-        <v>45.64928302601693</v>
+        <v>45.71850773357846</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9512790271431</v>
+        <v>99.95204639327326</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_35_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_35_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.74640658533961</v>
+        <v>45.48366784527518</v>
       </c>
       <c r="M2" t="n">
-        <v>98.68386969896602</v>
+        <v>99.68234065222777</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.98713047504685</v>
+        <v>88.08437258515248</v>
       </c>
       <c r="C3" t="n">
-        <v>45.9290713409773</v>
+        <v>45.93901385449821</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228627211548904</v>
+        <v>2.228869081312118</v>
       </c>
       <c r="E3" t="n">
-        <v>5.704294349918538</v>
+        <v>5.715427997200841</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428757371829682</v>
+        <v>0.7429563604373727</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97369361454665</v>
+        <v>33.9760997303247</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17228391041653</v>
+        <v>34.17599258011914</v>
       </c>
       <c r="I3" t="n">
-        <v>6.522382294039708</v>
+        <v>6.601549583024741</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642973357393551</v>
+        <v>4.643477252733579</v>
       </c>
       <c r="K3" t="n">
-        <v>12.01286952495315</v>
+        <v>11.91562741484751</v>
       </c>
       <c r="L3" t="n">
-        <v>48.82392819426085</v>
+        <v>48.90841167482672</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7658690601913</v>
+        <v>106.7630529441724</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.96727312750544</v>
+        <v>87.16658941541749</v>
       </c>
       <c r="C4" t="n">
-        <v>42.53551999538339</v>
+        <v>42.66245188607124</v>
       </c>
       <c r="D4" t="n">
-        <v>2.178929707885865</v>
+        <v>2.184667376852732</v>
       </c>
       <c r="E4" t="n">
-        <v>6.48486843211248</v>
+        <v>6.520897615653437</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444265871037126</v>
+        <v>0.7445226470933273</v>
       </c>
       <c r="G4" t="n">
-        <v>33.21609370994778</v>
+        <v>33.30230442688843</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24362300677078</v>
+        <v>34.24804176629305</v>
       </c>
       <c r="I4" t="n">
-        <v>5.446665514286615</v>
+        <v>5.512889038303235</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652666169398204</v>
+        <v>4.653266544333295</v>
       </c>
       <c r="K4" t="n">
-        <v>13.03272687249457</v>
+        <v>12.83341058458251</v>
       </c>
       <c r="L4" t="n">
-        <v>44.25057584617651</v>
+        <v>44.32076115203999</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81882271405446</v>
+        <v>99.81662362269374</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.59941409996046</v>
+        <v>86.14150179208472</v>
       </c>
       <c r="C5" t="n">
-        <v>42.01294073093354</v>
+        <v>42.49298347625281</v>
       </c>
       <c r="D5" t="n">
-        <v>2.11149469999921</v>
+        <v>2.135152231730974</v>
       </c>
       <c r="E5" t="n">
-        <v>7.041991048979308</v>
+        <v>7.140145112053638</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457446847343752</v>
+        <v>0.7458485599049327</v>
       </c>
       <c r="G5" t="n">
-        <v>32.18809930829838</v>
+        <v>32.54751289475053</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30425549778126</v>
+        <v>34.3090337556269</v>
       </c>
       <c r="I5" t="n">
-        <v>4.546924580578082</v>
+        <v>4.602255738611913</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660904279589845</v>
+        <v>4.661553499405829</v>
       </c>
       <c r="K5" t="n">
-        <v>14.40058590003955</v>
+        <v>13.85849820791529</v>
       </c>
       <c r="L5" t="n">
-        <v>43.43517710474116</v>
+        <v>43.49538250921238</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84870373571425</v>
+        <v>99.84686419338047</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.04063239227523</v>
+        <v>84.90015546901661</v>
       </c>
       <c r="C6" t="n">
-        <v>41.16006533718414</v>
+        <v>41.9665146612903</v>
       </c>
       <c r="D6" t="n">
-        <v>2.034939214089274</v>
+        <v>2.0749029347059</v>
       </c>
       <c r="E6" t="n">
-        <v>7.419140668995332</v>
+        <v>7.578832062089212</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468671406436811</v>
+        <v>0.7469733328444854</v>
       </c>
       <c r="G6" t="n">
-        <v>31.02107029180832</v>
+        <v>31.62909371007559</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35588846960933</v>
+        <v>34.36077331084632</v>
       </c>
       <c r="I6" t="n">
-        <v>3.794806978106293</v>
+        <v>3.840996788177061</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667919629023007</v>
+        <v>4.668583330278033</v>
       </c>
       <c r="K6" t="n">
-        <v>15.95936760772475</v>
+        <v>15.0998445309834</v>
       </c>
       <c r="L6" t="n">
-        <v>42.7542635945195</v>
+        <v>42.80580037054266</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87369653942839</v>
+        <v>99.87215956281635</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.21955435419916</v>
+        <v>83.43652530406553</v>
       </c>
       <c r="C7" t="n">
-        <v>39.92799580219751</v>
+        <v>41.09964365089982</v>
       </c>
       <c r="D7" t="n">
-        <v>1.945876971754638</v>
+        <v>2.003902378920194</v>
       </c>
       <c r="E7" t="n">
-        <v>7.622163690710739</v>
+        <v>7.853648834401294</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478259065394706</v>
+        <v>0.7479297470986873</v>
       </c>
       <c r="G7" t="n">
-        <v>29.66338547219305</v>
+        <v>30.54678610192146</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39999170081564</v>
+        <v>34.40476836653961</v>
       </c>
       <c r="I7" t="n">
-        <v>3.166398696313941</v>
+        <v>3.204928955817484</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673911915871691</v>
+        <v>4.674560919366796</v>
       </c>
       <c r="K7" t="n">
-        <v>17.78044564580084</v>
+        <v>16.56347469593447</v>
       </c>
       <c r="L7" t="n">
-        <v>42.18614724705424</v>
+        <v>42.23018729793857</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89458869505258</v>
+        <v>99.89330564477285</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.16927196563672</v>
+        <v>88.29701290607811</v>
       </c>
       <c r="C8" t="n">
-        <v>42.271557855287</v>
+        <v>43.42189247849075</v>
       </c>
       <c r="D8" t="n">
-        <v>1.950079730787592</v>
+        <v>2.00815446586985</v>
       </c>
       <c r="E8" t="n">
-        <v>9.483915134927503</v>
+        <v>9.698870607973205</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494410816658568</v>
+        <v>0.7495167816520426</v>
       </c>
       <c r="G8" t="n">
-        <v>30.17942119053908</v>
+        <v>31.05748767731495</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47428975662941</v>
+        <v>34.47777195599395</v>
       </c>
       <c r="I8" t="n">
-        <v>5.648118310675677</v>
+        <v>5.62073153194886</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684006760411605</v>
+        <v>4.684479885325266</v>
       </c>
       <c r="K8" t="n">
-        <v>12.83072803436326</v>
+        <v>11.70298709392187</v>
       </c>
       <c r="L8" t="n">
-        <v>44.70984925571548</v>
+        <v>44.68815942301701</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81213514536574</v>
+        <v>99.81303899542965</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84.88989757908038</v>
+        <v>86.40161842313027</v>
       </c>
       <c r="C9" t="n">
-        <v>40.86794362784642</v>
+        <v>42.39929220707729</v>
       </c>
       <c r="D9" t="n">
-        <v>1.84667713560545</v>
+        <v>1.922623976861939</v>
       </c>
       <c r="E9" t="n">
-        <v>9.766945784600862</v>
+        <v>10.06785069238522</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508287515708582</v>
+        <v>0.7508736425393977</v>
       </c>
       <c r="G9" t="n">
-        <v>28.57916330214171</v>
+        <v>29.7346999368573</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53812257225947</v>
+        <v>34.54018755681228</v>
       </c>
       <c r="I9" t="n">
-        <v>4.715480335584159</v>
+        <v>4.692422351802886</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692679697317864</v>
+        <v>4.692960265871235</v>
       </c>
       <c r="K9" t="n">
-        <v>15.11010242091962</v>
+        <v>13.59838157686974</v>
       </c>
       <c r="L9" t="n">
-        <v>43.86506177593741</v>
+        <v>43.84619478460993</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84310782470345</v>
+        <v>99.84386856855696</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.36751586894304</v>
+        <v>84.34741916561484</v>
       </c>
       <c r="C10" t="n">
-        <v>39.07616108816822</v>
+        <v>41.0735743177677</v>
       </c>
       <c r="D10" t="n">
-        <v>1.73354185765898</v>
+        <v>1.8307992222727</v>
       </c>
       <c r="E10" t="n">
-        <v>9.824552225715539</v>
+        <v>10.23974294055392</v>
       </c>
       <c r="F10" t="n">
-        <v>0.752024664479477</v>
+        <v>0.752035790180305</v>
       </c>
       <c r="G10" t="n">
-        <v>26.82828247878367</v>
+        <v>28.31456705734175</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59313456605594</v>
+        <v>34.59364634829402</v>
       </c>
       <c r="I10" t="n">
-        <v>3.935825923252694</v>
+        <v>3.91640411834522</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700154152996732</v>
+        <v>4.700223688626906</v>
       </c>
       <c r="K10" t="n">
-        <v>17.63248413105696</v>
+        <v>15.65258083438518</v>
       </c>
       <c r="L10" t="n">
-        <v>43.16036921589747</v>
+        <v>43.14349978251926</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86901443512266</v>
+        <v>99.86965493467214</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>79.84549056877036</v>
+        <v>82.22802973793704</v>
       </c>
       <c r="C11" t="n">
-        <v>37.16301841580562</v>
+        <v>39.56170059910774</v>
       </c>
       <c r="D11" t="n">
-        <v>1.621867077650598</v>
+        <v>1.737017938430957</v>
       </c>
       <c r="E11" t="n">
-        <v>9.739046500866616</v>
+        <v>10.25988559182315</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530557866803954</v>
+        <v>0.7530320636884162</v>
       </c>
       <c r="G11" t="n">
-        <v>25.10000431198657</v>
+        <v>26.86417510952111</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64056618729819</v>
+        <v>34.63947492966714</v>
       </c>
       <c r="I11" t="n">
-        <v>3.284352037535506</v>
+        <v>3.267993706753671</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706598666752472</v>
+        <v>4.706450398052601</v>
       </c>
       <c r="K11" t="n">
-        <v>20.15450943122965</v>
+        <v>17.77197026206296</v>
       </c>
       <c r="L11" t="n">
-        <v>42.57314365509659</v>
+        <v>42.55754013554195</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89067150213187</v>
+        <v>99.89121099671263</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.29191646194039</v>
+        <v>80.02759556649342</v>
       </c>
       <c r="C12" t="n">
-        <v>35.11655957556748</v>
+        <v>37.86756454684692</v>
       </c>
       <c r="D12" t="n">
-        <v>1.510060526282853</v>
+        <v>1.64052351650147</v>
       </c>
       <c r="E12" t="n">
-        <v>9.524365521746565</v>
+        <v>10.14433423945522</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539457112554865</v>
+        <v>0.7538872196408197</v>
       </c>
       <c r="G12" t="n">
-        <v>23.36968685249171</v>
+        <v>25.3718226182467</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68150271775238</v>
+        <v>34.6788121034777</v>
       </c>
       <c r="I12" t="n">
-        <v>2.740194437064603</v>
+        <v>2.726420746416397</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712160695346791</v>
+        <v>4.711795122755122</v>
       </c>
       <c r="K12" t="n">
-        <v>22.70808353805963</v>
+        <v>19.97240443350656</v>
       </c>
       <c r="L12" t="n">
-        <v>42.08412488533025</v>
+        <v>42.06925341668114</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90876799895734</v>
+        <v>99.90922239703463</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>74.78548133231035</v>
+        <v>77.7581006181815</v>
       </c>
       <c r="C13" t="n">
-        <v>33.03220604285001</v>
+        <v>36.01974219364565</v>
       </c>
       <c r="D13" t="n">
-        <v>1.401474843328915</v>
+        <v>1.541823576324642</v>
       </c>
       <c r="E13" t="n">
-        <v>9.220456176535274</v>
+        <v>9.913052428886429</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547138574982276</v>
+        <v>0.7546221975898334</v>
       </c>
       <c r="G13" t="n">
-        <v>21.68921553155464</v>
+        <v>23.84536027289831</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71683744491847</v>
+        <v>34.71262108913233</v>
       </c>
       <c r="I13" t="n">
-        <v>2.285821869110917</v>
+        <v>2.274232318413496</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716961609363922</v>
+        <v>4.716388734936457</v>
       </c>
       <c r="K13" t="n">
-        <v>25.21451866768964</v>
+        <v>22.24189938181852</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67715877731967</v>
+        <v>41.66262451491315</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92388348785931</v>
+        <v>99.9242660903773</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.25083599276627</v>
+        <v>84.24852567379881</v>
       </c>
       <c r="C14" t="n">
-        <v>37.82011592898806</v>
+        <v>40.05683129637089</v>
       </c>
       <c r="D14" t="n">
-        <v>1.403042867591186</v>
+        <v>1.543599006220875</v>
       </c>
       <c r="E14" t="n">
-        <v>11.84062330376986</v>
+        <v>12.17029119182213</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555582605535249</v>
+        <v>0.7554911548625945</v>
       </c>
       <c r="G14" t="n">
-        <v>23.86320610561665</v>
+        <v>25.63357590555588</v>
       </c>
       <c r="H14" t="n">
-        <v>36.90540382627169</v>
+        <v>36.51335051392512</v>
       </c>
       <c r="I14" t="n">
-        <v>2.760762500503835</v>
+        <v>2.910398183520989</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722239128459531</v>
+        <v>4.721819717891214</v>
       </c>
       <c r="K14" t="n">
-        <v>17.74916400723372</v>
+        <v>15.75147432620119</v>
       </c>
       <c r="L14" t="n">
-        <v>44.33879749362172</v>
+        <v>44.09479268819905</v>
       </c>
       <c r="M14" t="n">
-        <v>99.9080774298435</v>
+        <v>99.90309831077113</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.41081338710453</v>
+        <v>83.65348839025484</v>
       </c>
       <c r="C15" t="n">
-        <v>37.40034610841444</v>
+        <v>39.91214194485096</v>
       </c>
       <c r="D15" t="n">
-        <v>1.371949245407459</v>
+        <v>1.521726351773158</v>
       </c>
       <c r="E15" t="n">
-        <v>11.96752360810548</v>
+        <v>12.40245229278204</v>
       </c>
       <c r="F15" t="n">
-        <v>0.756270656931783</v>
+        <v>0.7562219828184495</v>
       </c>
       <c r="G15" t="n">
-        <v>23.33986641878179</v>
+        <v>25.27035051749721</v>
       </c>
       <c r="H15" t="n">
-        <v>36.94570722522668</v>
+        <v>36.54867187691627</v>
       </c>
       <c r="I15" t="n">
-        <v>2.302804626827712</v>
+        <v>2.427677975852398</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726691605823644</v>
+        <v>4.726387392615308</v>
       </c>
       <c r="K15" t="n">
-        <v>18.58918661289546</v>
+        <v>16.34651160974518</v>
       </c>
       <c r="L15" t="n">
-        <v>43.93377943145389</v>
+        <v>43.66050205141716</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92331215276378</v>
+        <v>99.91915560601329</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.79580074964161</v>
+        <v>81.44517455675319</v>
       </c>
       <c r="C16" t="n">
-        <v>35.14043126771186</v>
+        <v>38.07961480801537</v>
       </c>
       <c r="D16" t="n">
-        <v>1.275172843334192</v>
+        <v>1.437178601597615</v>
       </c>
       <c r="E16" t="n">
-        <v>11.4434361530126</v>
+        <v>12.0508237819422</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568850997535759</v>
+        <v>0.7568486432246709</v>
       </c>
       <c r="G16" t="n">
-        <v>21.69348751340943</v>
+        <v>23.86631931312712</v>
       </c>
       <c r="H16" t="n">
-        <v>36.97572428908143</v>
+        <v>36.57895875839501</v>
       </c>
       <c r="I16" t="n">
-        <v>1.920562977590516</v>
+        <v>2.02474143831236</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730531873459849</v>
+        <v>4.730304020154191</v>
       </c>
       <c r="K16" t="n">
-        <v>21.2041992503584</v>
+        <v>18.55482544324683</v>
       </c>
       <c r="L16" t="n">
-        <v>43.59140268674008</v>
+        <v>43.29812424940858</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93603320481034</v>
+        <v>99.93256450067078</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.75932561056635</v>
+        <v>83.11774866804735</v>
       </c>
       <c r="C17" t="n">
-        <v>36.57598851962146</v>
+        <v>39.30346620574893</v>
       </c>
       <c r="D17" t="n">
-        <v>1.276156212211828</v>
+        <v>1.438337643043708</v>
       </c>
       <c r="E17" t="n">
-        <v>12.3120038516571</v>
+        <v>12.82475104802514</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574687831773051</v>
+        <v>0.7574590189601165</v>
       </c>
       <c r="G17" t="n">
-        <v>22.25856580084009</v>
+        <v>24.31461556263771</v>
       </c>
       <c r="H17" t="n">
-        <v>37.55258770517477</v>
+        <v>37.03750737040941</v>
       </c>
       <c r="I17" t="n">
-        <v>1.868363362647091</v>
+        <v>2.010959156470547</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734179894858157</v>
+        <v>4.734118868500726</v>
       </c>
       <c r="K17" t="n">
-        <v>19.24067438943365</v>
+        <v>16.88225133195266</v>
       </c>
       <c r="L17" t="n">
-        <v>44.12110630240636</v>
+        <v>43.74730450612927</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93776921146147</v>
+        <v>99.93302204383085</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.24396036508446</v>
+        <v>80.98811209556405</v>
       </c>
       <c r="C18" t="n">
-        <v>34.34832431388321</v>
+        <v>37.48482658302649</v>
       </c>
       <c r="D18" t="n">
-        <v>1.187395909417343</v>
+        <v>1.359873859846114</v>
       </c>
       <c r="E18" t="n">
-        <v>11.7153360309958</v>
+        <v>12.40463155902982</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579715434098977</v>
+        <v>0.7579818221929809</v>
       </c>
       <c r="G18" t="n">
-        <v>20.71041909172419</v>
+        <v>22.98821161759287</v>
       </c>
       <c r="H18" t="n">
-        <v>37.57751275574901</v>
+        <v>37.06307090336077</v>
       </c>
       <c r="I18" t="n">
-        <v>1.558002887476345</v>
+        <v>1.676955944835374</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737322146311861</v>
+        <v>4.737386388706129</v>
       </c>
       <c r="K18" t="n">
-        <v>21.75603963491553</v>
+        <v>19.01188790443597</v>
       </c>
       <c r="L18" t="n">
-        <v>43.8437370689055</v>
+        <v>43.44742553596892</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94810101770425</v>
+        <v>99.94414002343137</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.26541315835351</v>
+        <v>80.16543697183636</v>
       </c>
       <c r="C19" t="n">
-        <v>33.59943706998152</v>
+        <v>36.92093428282787</v>
       </c>
       <c r="D19" t="n">
-        <v>1.153088002585927</v>
+        <v>1.330207307910479</v>
       </c>
       <c r="E19" t="n">
-        <v>11.5948891211554</v>
+        <v>12.3670622432788</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583993543262201</v>
+        <v>0.7584225223547694</v>
       </c>
       <c r="G19" t="n">
-        <v>20.11202463625812</v>
+        <v>22.48670850469543</v>
       </c>
       <c r="H19" t="n">
-        <v>37.59872208782081</v>
+        <v>37.08461983879069</v>
       </c>
       <c r="I19" t="n">
-        <v>1.308293991668159</v>
+        <v>1.39827579008887</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739995964538876</v>
+        <v>4.740140764717307</v>
       </c>
       <c r="K19" t="n">
-        <v>22.73458684164649</v>
+        <v>19.83456302816367</v>
       </c>
       <c r="L19" t="n">
-        <v>43.62239088881355</v>
+        <v>43.19792057942971</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95641480044156</v>
+        <v>99.95341789042125</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.67521910285394</v>
+        <v>77.82398833216178</v>
       </c>
       <c r="C20" t="n">
-        <v>31.2099145576689</v>
+        <v>34.7951569094106</v>
       </c>
       <c r="D20" t="n">
-        <v>1.062712866457483</v>
+        <v>1.244751442662674</v>
       </c>
       <c r="E20" t="n">
-        <v>10.86791691536946</v>
+        <v>11.76687298462794</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587686172471644</v>
+        <v>0.7588012307043275</v>
       </c>
       <c r="G20" t="n">
-        <v>18.5357121950184</v>
+        <v>21.04210575712637</v>
       </c>
       <c r="H20" t="n">
-        <v>37.61702882010206</v>
+        <v>37.10313755781824</v>
       </c>
       <c r="I20" t="n">
-        <v>1.09077583086459</v>
+        <v>1.165811667320171</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742303857794778</v>
+        <v>4.742507691902046</v>
       </c>
       <c r="K20" t="n">
-        <v>25.32478089714606</v>
+        <v>22.17601166783823</v>
       </c>
       <c r="L20" t="n">
-        <v>43.42896304541649</v>
+        <v>42.98999042858205</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96365850023145</v>
+        <v>99.96115900583088</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.07247367578995</v>
+        <v>83.22932429463499</v>
       </c>
       <c r="C21" t="n">
-        <v>35.30601233548475</v>
+        <v>38.11128824258108</v>
       </c>
       <c r="D21" t="n">
-        <v>1.063341823158715</v>
+        <v>1.245603719140352</v>
       </c>
       <c r="E21" t="n">
-        <v>13.035962452236</v>
+        <v>13.56790444119739</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592176873784906</v>
+        <v>0.7593207789595027</v>
       </c>
       <c r="G21" t="n">
-        <v>20.46838590691751</v>
+        <v>22.56455395430402</v>
       </c>
       <c r="H21" t="n">
-        <v>39.5609956313307</v>
+        <v>38.63658268108234</v>
       </c>
       <c r="I21" t="n">
-        <v>1.439459628652965</v>
+        <v>1.709603851454489</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745110546115567</v>
+        <v>4.745754868496891</v>
       </c>
       <c r="K21" t="n">
-        <v>18.92752632421004</v>
+        <v>16.77067570536501</v>
       </c>
       <c r="L21" t="n">
-        <v>45.71850773357846</v>
+        <v>45.061088248945</v>
       </c>
       <c r="M21" t="n">
-        <v>99.95204639327326</v>
+        <v>99.94305219689109</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_35_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_35_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.48366784527518</v>
+        <v>43.1809587416778</v>
       </c>
       <c r="M2" t="n">
-        <v>99.68234065222777</v>
+        <v>96.47636503603911</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.08437258515248</v>
+        <v>81.58720950082909</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93901385449821</v>
+        <v>43.34276505638466</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228869081312118</v>
+        <v>2.186429307852579</v>
       </c>
       <c r="E3" t="n">
-        <v>5.715427997200841</v>
+        <v>4.156347968165782</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429563604373727</v>
+        <v>0.7377107353125375</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9760997303247</v>
+        <v>32.88754083894921</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17599258011914</v>
+        <v>33.93469382437672</v>
       </c>
       <c r="I3" t="n">
-        <v>6.601549583024741</v>
+        <v>3.073794730468906</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643477252733579</v>
+        <v>4.610692095703359</v>
       </c>
       <c r="K3" t="n">
-        <v>11.91562741484751</v>
+        <v>18.41279049917089</v>
       </c>
       <c r="L3" t="n">
-        <v>48.90841167482672</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7630529441724</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.16658941541749</v>
+        <v>88.70937167374461</v>
       </c>
       <c r="C4" t="n">
-        <v>42.66245188607124</v>
+        <v>42.91124316033798</v>
       </c>
       <c r="D4" t="n">
-        <v>2.184667376852732</v>
+        <v>2.192210979395547</v>
       </c>
       <c r="E4" t="n">
-        <v>6.520897615653437</v>
+        <v>6.525633749926459</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445226470933273</v>
+        <v>0.7396614963776128</v>
       </c>
       <c r="G4" t="n">
-        <v>33.30230442688843</v>
+        <v>33.5672090293283</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24804176629305</v>
+        <v>34.02442883337019</v>
       </c>
       <c r="I4" t="n">
-        <v>5.512889038303235</v>
+        <v>7.037343232986427</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653266544333295</v>
+        <v>4.62288435236008</v>
       </c>
       <c r="K4" t="n">
-        <v>12.83341058458251</v>
+        <v>11.29062832625537</v>
       </c>
       <c r="L4" t="n">
-        <v>44.32076115203999</v>
+        <v>45.56416907491223</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81662362269374</v>
+        <v>99.76604056150559</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.14150179208472</v>
+        <v>87.76084094499416</v>
       </c>
       <c r="C5" t="n">
-        <v>42.49298347625281</v>
+        <v>43.05359330863664</v>
       </c>
       <c r="D5" t="n">
-        <v>2.135152231730974</v>
+        <v>2.147819830228094</v>
       </c>
       <c r="E5" t="n">
-        <v>7.140145112053638</v>
+        <v>7.373083769054554</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458485599049327</v>
+        <v>0.7413127238703845</v>
       </c>
       <c r="G5" t="n">
-        <v>32.54751289475053</v>
+        <v>32.88749024442975</v>
       </c>
       <c r="H5" t="n">
-        <v>34.3090337556269</v>
+        <v>34.10038529803769</v>
       </c>
       <c r="I5" t="n">
-        <v>4.602255738611913</v>
+        <v>5.877544555183776</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661553499405829</v>
+        <v>4.633204524189903</v>
       </c>
       <c r="K5" t="n">
-        <v>13.85849820791529</v>
+        <v>12.23915905500587</v>
       </c>
       <c r="L5" t="n">
-        <v>43.49538250921238</v>
+        <v>44.51176587988562</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84686419338047</v>
+        <v>99.80451824352812</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.90015546901661</v>
+        <v>86.53797335640385</v>
       </c>
       <c r="C6" t="n">
-        <v>41.9665146612903</v>
+        <v>42.74316461165694</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0749029347059</v>
+        <v>2.089829087900491</v>
       </c>
       <c r="E6" t="n">
-        <v>7.578832062089212</v>
+        <v>7.991880504789367</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469733328444854</v>
+        <v>0.7427139502032252</v>
       </c>
       <c r="G6" t="n">
-        <v>31.62909371007559</v>
+        <v>31.99953402681547</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36077331084632</v>
+        <v>34.16484170934836</v>
       </c>
       <c r="I6" t="n">
-        <v>3.840996788177061</v>
+        <v>4.907211888576798</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668583330278033</v>
+        <v>4.641962188770157</v>
       </c>
       <c r="K6" t="n">
-        <v>15.0998445309834</v>
+        <v>13.46202664359613</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80580037054266</v>
+        <v>43.63154361821407</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87215956281635</v>
+        <v>99.83673487346714</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.43652530406553</v>
+        <v>85.1505179892754</v>
       </c>
       <c r="C7" t="n">
-        <v>41.09964365089982</v>
+        <v>42.11805940932689</v>
       </c>
       <c r="D7" t="n">
-        <v>2.003902378920194</v>
+        <v>2.024165941138801</v>
       </c>
       <c r="E7" t="n">
-        <v>7.853648834401294</v>
+        <v>8.423422890948352</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479297470986873</v>
+        <v>0.7439048148030775</v>
       </c>
       <c r="G7" t="n">
-        <v>30.54678610192146</v>
+        <v>30.99409769172292</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40476836653961</v>
+        <v>34.21962148094156</v>
       </c>
       <c r="I7" t="n">
-        <v>3.204928955817484</v>
+        <v>4.095900077201453</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674560919366796</v>
+        <v>4.649405092519234</v>
       </c>
       <c r="K7" t="n">
-        <v>16.56347469593447</v>
+        <v>14.84948201072458</v>
       </c>
       <c r="L7" t="n">
-        <v>42.23018729793857</v>
+        <v>42.89614713859918</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89330564477285</v>
+        <v>99.86368855865067</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.29701290607811</v>
+        <v>83.61399793370794</v>
       </c>
       <c r="C8" t="n">
-        <v>43.42189247849075</v>
+        <v>41.21794629376808</v>
       </c>
       <c r="D8" t="n">
-        <v>2.00815446586985</v>
+        <v>1.951772403089258</v>
       </c>
       <c r="E8" t="n">
-        <v>9.698870607973205</v>
+        <v>8.691812464220039</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495167816520426</v>
+        <v>0.7449184381076394</v>
       </c>
       <c r="G8" t="n">
-        <v>31.05748767731495</v>
+        <v>29.88560537646609</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47777195599395</v>
+        <v>34.26624815295141</v>
       </c>
       <c r="I8" t="n">
-        <v>5.62073153194886</v>
+        <v>3.417900860700774</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684479885325266</v>
+        <v>4.655740238172745</v>
       </c>
       <c r="K8" t="n">
-        <v>11.70298709392187</v>
+        <v>16.38600206629207</v>
       </c>
       <c r="L8" t="n">
-        <v>44.68815942301701</v>
+        <v>42.28227663779533</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81303899542965</v>
+        <v>99.88622499785549</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.40161842313027</v>
+        <v>81.85464747907929</v>
       </c>
       <c r="C9" t="n">
-        <v>42.39929220707729</v>
+        <v>39.98946668012949</v>
       </c>
       <c r="D9" t="n">
-        <v>1.922623976861939</v>
+        <v>1.869215075755781</v>
       </c>
       <c r="E9" t="n">
-        <v>10.06785069238522</v>
+        <v>8.799420275155571</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508736425393977</v>
+        <v>0.7457834585375975</v>
       </c>
       <c r="G9" t="n">
-        <v>29.7346999368573</v>
+        <v>28.62148477422842</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54018755681228</v>
+        <v>34.30603909272948</v>
       </c>
       <c r="I9" t="n">
-        <v>4.692422351802886</v>
+        <v>2.851558186812445</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692960265871235</v>
+        <v>4.661146615859984</v>
       </c>
       <c r="K9" t="n">
-        <v>13.59838157686974</v>
+        <v>18.14535252092072</v>
       </c>
       <c r="L9" t="n">
-        <v>43.84619478460993</v>
+        <v>41.7702391083748</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84386856855696</v>
+        <v>99.905058309425</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.34741916561484</v>
+        <v>86.2839537365826</v>
       </c>
       <c r="C10" t="n">
-        <v>41.0735743177677</v>
+        <v>42.99353695517391</v>
       </c>
       <c r="D10" t="n">
-        <v>1.8307992222727</v>
+        <v>1.871379686851986</v>
       </c>
       <c r="E10" t="n">
-        <v>10.23974294055392</v>
+        <v>10.53993846402472</v>
       </c>
       <c r="F10" t="n">
-        <v>0.752035790180305</v>
+        <v>0.7466470997368659</v>
       </c>
       <c r="G10" t="n">
-        <v>28.31456705734175</v>
+        <v>29.88535960129053</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59364634829402</v>
+        <v>35.57649681627815</v>
       </c>
       <c r="I10" t="n">
-        <v>3.91640411834522</v>
+        <v>2.997587695044942</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700223688626906</v>
+        <v>4.666544373355412</v>
       </c>
       <c r="K10" t="n">
-        <v>15.65258083438518</v>
+        <v>13.7160462634174</v>
       </c>
       <c r="L10" t="n">
-        <v>43.14349978251926</v>
+        <v>43.19061276782726</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86965493467214</v>
+        <v>99.90019598641857</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.22802973793704</v>
+        <v>86.10051417804408</v>
       </c>
       <c r="C11" t="n">
-        <v>39.56170059910774</v>
+        <v>43.20284463946202</v>
       </c>
       <c r="D11" t="n">
-        <v>1.737017938430957</v>
+        <v>1.859279948917706</v>
       </c>
       <c r="E11" t="n">
-        <v>10.25988559182315</v>
+        <v>10.92148680808348</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530320636884162</v>
+        <v>0.7473833862221537</v>
       </c>
       <c r="G11" t="n">
-        <v>26.86417510952111</v>
+        <v>29.71729785014609</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63947492966714</v>
+        <v>35.63674699936915</v>
       </c>
       <c r="I11" t="n">
-        <v>3.267993706753671</v>
+        <v>2.547173021417045</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706450398052601</v>
+        <v>4.67114616388846</v>
       </c>
       <c r="K11" t="n">
-        <v>17.77197026206296</v>
+        <v>13.89948582195592</v>
       </c>
       <c r="L11" t="n">
-        <v>42.55754013554195</v>
+        <v>42.81284741631618</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89121099671263</v>
+        <v>99.91517787773412</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.02759556649342</v>
+        <v>84.30222727322112</v>
       </c>
       <c r="C12" t="n">
-        <v>37.86756454684692</v>
+        <v>41.80093511929883</v>
       </c>
       <c r="D12" t="n">
-        <v>1.64052351650147</v>
+        <v>1.782101052245717</v>
       </c>
       <c r="E12" t="n">
-        <v>10.14433423945522</v>
+        <v>10.82220600064202</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538872196408197</v>
+        <v>0.7480111915431745</v>
       </c>
       <c r="G12" t="n">
-        <v>25.3718226182467</v>
+        <v>28.48372984362708</v>
       </c>
       <c r="H12" t="n">
-        <v>34.6788121034777</v>
+        <v>35.66668202308324</v>
       </c>
       <c r="I12" t="n">
-        <v>2.726420746416397</v>
+        <v>2.124427214935054</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711795122755122</v>
+        <v>4.67506994714484</v>
       </c>
       <c r="K12" t="n">
-        <v>19.97240443350656</v>
+        <v>15.69777272677888</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06925341668114</v>
+        <v>42.43053734777181</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90922239703463</v>
+        <v>99.92924519384951</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.7581006181815</v>
+        <v>85.41863149258243</v>
       </c>
       <c r="C13" t="n">
-        <v>36.01974219364565</v>
+        <v>42.74112563156105</v>
       </c>
       <c r="D13" t="n">
-        <v>1.541823576324642</v>
+        <v>1.783480708452063</v>
       </c>
       <c r="E13" t="n">
-        <v>9.913052428886429</v>
+        <v>11.44879558387824</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546221975898334</v>
+        <v>0.7485902823200575</v>
       </c>
       <c r="G13" t="n">
-        <v>23.84536027289831</v>
+        <v>28.79334812285871</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71262108913233</v>
+        <v>35.98186115675787</v>
       </c>
       <c r="I13" t="n">
-        <v>2.274232318413496</v>
+        <v>1.983866373815111</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716388734936457</v>
+        <v>4.678689264500359</v>
       </c>
       <c r="K13" t="n">
-        <v>22.24189938181852</v>
+        <v>14.58136850741758</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66262451491315</v>
+        <v>42.61142813754623</v>
       </c>
       <c r="M13" t="n">
-        <v>99.9242660903773</v>
+        <v>99.93392227652485</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.24852567379881</v>
+        <v>83.58529619471784</v>
       </c>
       <c r="C14" t="n">
-        <v>40.05683129637089</v>
+        <v>41.2164163960077</v>
       </c>
       <c r="D14" t="n">
-        <v>1.543599006220875</v>
+        <v>1.706803031979111</v>
       </c>
       <c r="E14" t="n">
-        <v>12.17029119182213</v>
+        <v>11.23229314393039</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554911548625945</v>
+        <v>0.7490841500363208</v>
       </c>
       <c r="G14" t="n">
-        <v>25.63357590555588</v>
+        <v>27.55542779017741</v>
       </c>
       <c r="H14" t="n">
-        <v>36.51335051392512</v>
+        <v>36.00559948200211</v>
       </c>
       <c r="I14" t="n">
-        <v>2.910398183520989</v>
+        <v>1.654312658865508</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721819717891214</v>
+        <v>4.681775937727004</v>
       </c>
       <c r="K14" t="n">
-        <v>15.75147432620119</v>
+        <v>16.41470380528216</v>
       </c>
       <c r="L14" t="n">
-        <v>44.09479268819905</v>
+        <v>42.31377239943749</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90309831077113</v>
+        <v>99.94489260072734</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.65348839025484</v>
+        <v>82.78009618012572</v>
       </c>
       <c r="C15" t="n">
-        <v>39.91214194485096</v>
+        <v>40.64842534810947</v>
       </c>
       <c r="D15" t="n">
-        <v>1.521726351773158</v>
+        <v>1.672839545761726</v>
       </c>
       <c r="E15" t="n">
-        <v>12.40245229278204</v>
+        <v>11.24186503122296</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562219828184495</v>
+        <v>0.7495059859165792</v>
       </c>
       <c r="G15" t="n">
-        <v>25.27035051749721</v>
+        <v>27.00710535669741</v>
       </c>
       <c r="H15" t="n">
-        <v>36.54867187691627</v>
+        <v>36.02587551340791</v>
       </c>
       <c r="I15" t="n">
-        <v>2.427677975852398</v>
+        <v>1.398492335140529</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726387392615308</v>
+        <v>4.684412411978618</v>
       </c>
       <c r="K15" t="n">
-        <v>16.34651160974518</v>
+        <v>17.21990381987426</v>
       </c>
       <c r="L15" t="n">
-        <v>43.66050205141716</v>
+        <v>42.08508065742637</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91915560601329</v>
+        <v>99.95340982541011</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.44517455675319</v>
+        <v>80.5071244428224</v>
       </c>
       <c r="C16" t="n">
-        <v>38.07961480801537</v>
+        <v>38.59257922884262</v>
       </c>
       <c r="D16" t="n">
-        <v>1.437178601597615</v>
+        <v>1.5783570447707</v>
       </c>
       <c r="E16" t="n">
-        <v>12.0508237819422</v>
+        <v>10.80124979238494</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568486432246709</v>
+        <v>0.7498678187647654</v>
       </c>
       <c r="G16" t="n">
-        <v>23.86631931312712</v>
+        <v>25.48173559538716</v>
       </c>
       <c r="H16" t="n">
-        <v>36.57895875839501</v>
+        <v>36.04326742940372</v>
       </c>
       <c r="I16" t="n">
-        <v>2.02474143831236</v>
+        <v>1.165972894831324</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730304020154191</v>
+        <v>4.686673867279782</v>
       </c>
       <c r="K16" t="n">
-        <v>18.55482544324683</v>
+        <v>19.49287555717761</v>
       </c>
       <c r="L16" t="n">
-        <v>43.29812424940858</v>
+        <v>41.87569820467031</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93256450067078</v>
+        <v>99.96115299069054</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>83.11774866804735</v>
+        <v>84.8365532787345</v>
       </c>
       <c r="C17" t="n">
-        <v>39.30346620574893</v>
+        <v>41.42278981013697</v>
       </c>
       <c r="D17" t="n">
-        <v>1.438337643043708</v>
+        <v>1.579191780225864</v>
       </c>
       <c r="E17" t="n">
-        <v>12.82475104802514</v>
+        <v>12.32566282415102</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574590189601165</v>
+        <v>0.7502643964954402</v>
       </c>
       <c r="G17" t="n">
-        <v>24.31461556263771</v>
+        <v>26.78957781149896</v>
       </c>
       <c r="H17" t="n">
-        <v>37.03750737040941</v>
+        <v>37.35669525436867</v>
       </c>
       <c r="I17" t="n">
-        <v>2.010959156470547</v>
+        <v>1.346008733898039</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734118868500726</v>
+        <v>4.689152478096499</v>
       </c>
       <c r="K17" t="n">
-        <v>16.88225133195266</v>
+        <v>15.16344672126552</v>
       </c>
       <c r="L17" t="n">
-        <v>43.74730450612927</v>
+        <v>43.36892022675544</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93302204383085</v>
+        <v>99.95515675815791</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.98811209556405</v>
+        <v>86.41782485353369</v>
       </c>
       <c r="C18" t="n">
-        <v>37.48482658302649</v>
+        <v>42.12180435036418</v>
       </c>
       <c r="D18" t="n">
-        <v>1.359873859846114</v>
+        <v>1.580519329506894</v>
       </c>
       <c r="E18" t="n">
-        <v>12.40463155902982</v>
+        <v>12.90888763556561</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579818221929809</v>
+        <v>0.7508951070732318</v>
       </c>
       <c r="G18" t="n">
-        <v>22.98821161759287</v>
+        <v>26.91691201868266</v>
       </c>
       <c r="H18" t="n">
-        <v>37.06307090336077</v>
+        <v>37.38809920070855</v>
       </c>
       <c r="I18" t="n">
-        <v>1.676955944835374</v>
+        <v>2.179417142789041</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737386388706129</v>
+        <v>4.693094419207697</v>
       </c>
       <c r="K18" t="n">
-        <v>19.01188790443597</v>
+        <v>13.58217514646631</v>
       </c>
       <c r="L18" t="n">
-        <v>43.44742553596892</v>
+        <v>44.2234342847597</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94414002343137</v>
+        <v>99.92741378159019</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>80.16543697183636</v>
+        <v>84.05095876579615</v>
       </c>
       <c r="C19" t="n">
-        <v>36.92093428282787</v>
+        <v>40.09304482847826</v>
       </c>
       <c r="D19" t="n">
-        <v>1.330207307910479</v>
+        <v>1.491247857563388</v>
       </c>
       <c r="E19" t="n">
-        <v>12.3670622432788</v>
+        <v>12.4826781196392</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584225223547694</v>
+        <v>0.751436343958895</v>
       </c>
       <c r="G19" t="n">
-        <v>22.48670850469543</v>
+        <v>25.39658113046042</v>
       </c>
       <c r="H19" t="n">
-        <v>37.08461983879069</v>
+        <v>37.41504812896982</v>
       </c>
       <c r="I19" t="n">
-        <v>1.39827579008887</v>
+        <v>1.817490035461349</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740140764717307</v>
+        <v>4.696477149743092</v>
       </c>
       <c r="K19" t="n">
-        <v>19.83456302816367</v>
+        <v>15.94904123420381</v>
       </c>
       <c r="L19" t="n">
-        <v>43.19792057942971</v>
+        <v>43.89737457224045</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95341789042125</v>
+        <v>99.93946063492253</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.82398833216178</v>
+        <v>81.57995869906921</v>
       </c>
       <c r="C20" t="n">
-        <v>34.7951569094106</v>
+        <v>37.90337255648679</v>
       </c>
       <c r="D20" t="n">
-        <v>1.244751442662674</v>
+        <v>1.398518562143754</v>
       </c>
       <c r="E20" t="n">
-        <v>11.76687298462794</v>
+        <v>11.95906135088738</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588012307043275</v>
+        <v>0.7519016590091329</v>
       </c>
       <c r="G20" t="n">
-        <v>21.04210575712637</v>
+        <v>23.81736204736103</v>
       </c>
       <c r="H20" t="n">
-        <v>37.10313755781824</v>
+        <v>37.4382168047196</v>
       </c>
       <c r="I20" t="n">
-        <v>1.165811667320171</v>
+        <v>1.515512906141244</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742507691902046</v>
+        <v>4.699385368807079</v>
       </c>
       <c r="K20" t="n">
-        <v>22.17601166783823</v>
+        <v>18.42004130093078</v>
       </c>
       <c r="L20" t="n">
-        <v>42.98999042858205</v>
+        <v>43.62610030826404</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96115900583088</v>
+        <v>99.94951416568161</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>83.22932429463499</v>
+        <v>79.02333059757785</v>
       </c>
       <c r="C21" t="n">
-        <v>38.11128824258108</v>
+        <v>35.58070342154065</v>
       </c>
       <c r="D21" t="n">
-        <v>1.245603719140352</v>
+        <v>1.303032558384513</v>
       </c>
       <c r="E21" t="n">
-        <v>13.56790444119739</v>
+        <v>11.35313815639748</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593207789595027</v>
+        <v>0.7523024281485752</v>
       </c>
       <c r="G21" t="n">
-        <v>22.56455395430402</v>
+        <v>22.19119505641068</v>
       </c>
       <c r="H21" t="n">
-        <v>38.63658268108234</v>
+        <v>37.45817165087708</v>
       </c>
       <c r="I21" t="n">
-        <v>1.709603851454489</v>
+        <v>1.263600571430926</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745754868496891</v>
+        <v>4.701890175928593</v>
       </c>
       <c r="K21" t="n">
-        <v>16.77067570536501</v>
+        <v>20.97666940242215</v>
       </c>
       <c r="L21" t="n">
-        <v>45.061088248945</v>
+        <v>43.40052959531105</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94305219689109</v>
+        <v>99.95790241927386</v>
       </c>
     </row>
   </sheetData>
